--- a/data/trans_orig/P1434-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,19 +526,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2007</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -733,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +688,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>12331</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5927</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>23894</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449882</t>
+          <t>452054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467849</t>
+          <t>467201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +766,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>444</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>461445</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>461445</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>449882</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>467849</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -984,70 +854,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>455</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>473776</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>473776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>473776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>473776</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>473776</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>473776</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1076,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +926,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>9019</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>16209</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350725</t>
+          <t>350040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362315</t>
+          <t>362403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1004,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357915</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>357915</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>350725</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>362315</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1327,70 +1092,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366934</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366934</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>366934</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>366934</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>366934</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1419,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1164,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12164</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>21485</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520904</t>
+          <t>522385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535711</t>
+          <t>536108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1242,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>519</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530225</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>530225</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>520904</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>535711</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1670,70 +1330,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>532</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>542389</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>542389</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>542389</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1762,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42368</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70118</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1402,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>54731</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>42368</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>70118</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1168216</t>
+          <t>1168644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1195966</t>
+          <t>1195397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1480,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1183603</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1168644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1195397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1183603</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1168216</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1195966</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,34%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -2013,70 +1568,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1238334</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1238334</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1238334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1238334</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1238334</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1238334</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2105,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26662</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +1640,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>10681</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>26662</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323893</t>
+          <t>325117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339874</t>
+          <t>340801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +1718,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333527</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>333527</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>323893</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>339874</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -2356,70 +1806,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350555</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350555</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>350555</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>350555</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>350555</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2453,7 +1868,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,77 +1883,42 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +1941,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293614</t>
+          <t>293587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +1956,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2586,70 +1966,35 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297287</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>297287</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>293614</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>298201</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
@@ -2699,70 +2044,35 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>306</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298201</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298201</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298201</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>298201</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>298201</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>298201</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2791,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87084</t>
+          <t>87704</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125757</t>
+          <t>125884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2116,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2816,70 +2126,35 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>106188</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>87084</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>125757</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
@@ -2904,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3144433</t>
+          <t>3144306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3183106</t>
+          <t>3182486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,77 +2199,42 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3164002</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3144306</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3182486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3096</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3164002</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3144433</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3183106</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>96,15%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -3042,70 +2282,35 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3270190</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3270190</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3270190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3207</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3270190</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3270190</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3270190</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3119,7 +2324,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3127,7 +2332,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3142,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3161,19 +2365,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2012</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3190,7 +2387,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3199,17 +2396,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3280,41 +2466,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3337,13 +2488,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3368,12 +2512,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,82 +2527,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>14779</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>8281</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>26459</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +2590,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408560</t>
+          <t>408782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426738</t>
+          <t>427410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,82 +2605,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>391</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>420240</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>420240</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>408560</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>426738</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -3619,70 +2693,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>435019</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>435019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>435019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>435019</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>435019</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>435019</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3711,12 +2750,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30637</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,82 +2765,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>19326</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>11846</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>30637</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +2828,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388160</t>
+          <t>389060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406951</t>
+          <t>407391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,82 +2843,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399471</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>389060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>407391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>399471</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>388160</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>406951</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3962,70 +2931,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>375</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>418797</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>418797</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>418797</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4054,12 +2988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,82 +3003,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>25721</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>16205</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>39044</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3066,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590371</t>
+          <t>589181</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613210</t>
+          <t>613033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,82 +3081,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>570</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>603694</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>589181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>613033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>603694</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>590371</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>613210</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -4305,70 +3169,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629415</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629415</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>629415</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>629415</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>629415</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4397,12 +3226,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29614</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>55839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,82 +3241,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>41113</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>29614</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>54009</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +3304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1105000</t>
+          <t>1103170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1129395</t>
+          <t>1128454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,82 +3319,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1117896</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1103170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1128454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1117896</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1105000</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1129395</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4648,70 +3407,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1159009</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1159009</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1159009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1159009</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1159009</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1159009</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4740,12 +3464,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,82 +3479,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>23469</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>15706</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>35654</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +3542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>474942</t>
+          <t>476443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>494890</t>
+          <t>495313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,82 +3557,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487127</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476443</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>487127</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>474942</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>494890</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -4991,70 +3645,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>487</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510596</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510596</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>510596</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>510596</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>510596</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5083,97 +3702,62 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5196,97 +3780,62 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>266882</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>266882</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>264956</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>266882</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -5334,70 +3883,35 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>265</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266882</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266882</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>266882</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>266882</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>266882</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5426,12 +3940,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102467</t>
+          <t>101106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146783</t>
+          <t>149196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,82 +3955,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>124409</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>102467</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>146783</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +4018,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3272935</t>
+          <t>3270522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3317251</t>
+          <t>3318612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,82 +4033,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3295309</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3270522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3318612</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3092</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3295309</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3272935</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3317251</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -5677,70 +4121,35 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3419718</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3419718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3419718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3419718</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3419718</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3419718</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5754,7 +4163,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5762,7 +4171,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5777,7 +4185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5796,19 +4204,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2016</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5825,7 +4226,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5834,17 +4235,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5915,41 +4305,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5972,13 +4327,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6003,12 +4351,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,82 +4366,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>14678</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>8530</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>23621</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +4429,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405471</t>
+          <t>405624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420562</t>
+          <t>420598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,82 +4444,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>381</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414414</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>420598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>414414</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>405471</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>420562</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -6254,70 +4532,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429092</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>429092</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>429092</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>429092</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6346,12 +4589,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,82 +4604,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>14622</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>8073</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>25675</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +4667,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351552</t>
+          <t>352946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369154</t>
+          <t>369256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,82 +4682,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>341</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362605</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>362605</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>351552</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>369154</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -6597,70 +4770,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>354</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377227</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>377227</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>377227</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>377227</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6689,12 +4827,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,82 +4842,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20463</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>20463</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>13242</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>29620</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +4905,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492294</t>
+          <t>491813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508672</t>
+          <t>508740</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,82 +4920,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>501451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>491813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>508740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>501451</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>492294</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>508672</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6940,70 +5008,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521914</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>521914</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>521914</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>521914</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7032,12 +5065,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39650</t>
+          <t>39114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,82 +5080,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>28245</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>19380</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>39650</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +5143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1109988</t>
+          <t>1110524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130258</t>
+          <t>1129776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,82 +5158,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1121393</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1110524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1129776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1121393</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1109988</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1130258</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -7283,70 +5246,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1149638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1149638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1149638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1149638</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1149638</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1149638</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7375,12 +5303,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>41523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,82 +5318,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>30994</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>22131</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>43187</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +5381,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>577519</t>
+          <t>579183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>598575</t>
+          <t>599618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,82 +5396,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>563</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>589712</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>579183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>589712</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>577519</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>598575</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -7626,70 +5484,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>597</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>620706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>620706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>620706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>620706</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>620706</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>620706</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7718,97 +5541,62 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -7831,97 +5619,62 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>287145</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>287145</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>285126</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>287145</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -7969,70 +5722,35 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287145</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287145</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>287145</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>287145</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>287145</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8061,12 +5779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91364</t>
+          <t>90174</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131852</t>
+          <t>130817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,82 +5794,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130817</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>109002</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>91364</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>131852</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +5857,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3253870</t>
+          <t>3254905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3294358</t>
+          <t>3295548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,82 +5872,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276720</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3254905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3295548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3276720</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3253870</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3294358</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -8312,70 +5960,35 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3385722</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3385722</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3385722</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3385722</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3385722</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3385722</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8389,7 +6002,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8397,7 +6010,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -8412,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8431,19 +6043,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2023</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8460,7 +6065,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8469,17 +6074,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8550,41 +6144,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8607,13 +6166,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8638,12 +6190,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38785</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,82 +6205,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>28629</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>21112</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>38785</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +6268,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461307</t>
+          <t>461426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>478980</t>
+          <t>478811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,82 +6283,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471463</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>461426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>478811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>471463</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>461307</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>478980</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -8889,70 +6371,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>500092</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>500092</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>500092</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8981,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,82 +6443,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>27927</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>38093</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +6506,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413024</t>
+          <t>412457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430785</t>
+          <t>431186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,82 +6521,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>423190</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>423190</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>413024</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>430785</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -9232,70 +6609,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451117</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451117</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>451117</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>451117</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>451117</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9324,12 +6666,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49171</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,82 +6681,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>28217</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>9107</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>49171</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +6744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617628</t>
+          <t>616135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657692</t>
+          <t>656181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,82 +6759,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>638582</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>656181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>638582</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>617628</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>657692</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -9575,70 +6847,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>486</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666799</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>666799</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>666799</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>666799</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9667,12 +6904,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78178</t>
+          <t>76978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,82 +6919,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63368</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>63368</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>51425</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>78178</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +6982,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>947868</t>
+          <t>949068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>974621</t>
+          <t>974448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,82 +6997,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>962678</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>949068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>974448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>962678</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>947868</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>974621</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -9918,70 +7085,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026046</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026046</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026046</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1026046</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1026046</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1026046</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10010,12 +7142,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,82 +7157,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27158</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>27158</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>20562</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>37615</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +7220,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434078</t>
+          <t>435150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451131</t>
+          <t>451827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,82 +7235,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>498</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444535</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>435150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>444535</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>434078</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>451131</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -10261,70 +7323,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>544</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471693</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>471693</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>471693</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>471693</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10358,7 +7385,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,77 +7400,42 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +7458,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235978</t>
+          <t>235381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +7473,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10491,70 +7483,35 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239270</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>239270</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>235978</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>240507</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
@@ -10604,70 +7561,35 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240507</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240507</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240507</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>240507</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>240507</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>240507</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10696,12 +7618,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139085</t>
+          <t>138563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201909</t>
+          <t>204154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,82 +7633,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176535</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>176535</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>139085</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>201909</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +7696,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3154346</t>
+          <t>3152101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3217170</t>
+          <t>3217692</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,82 +7711,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3179720</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3152101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3217692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3179720</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3154346</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3217170</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -10947,70 +7799,35 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3356255</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3356255</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3356255</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3356255</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3356255</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3356255</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11024,7 +7841,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11032,7 +7849,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P1434-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452054</t>
+          <t>451903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467201</t>
+          <t>467653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452054</t>
+          <t>451903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467201</t>
+          <t>467653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350040</t>
+          <t>350460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362403</t>
+          <t>362535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350040</t>
+          <t>350460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362403</t>
+          <t>362535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522385</t>
+          <t>521418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536108</t>
+          <t>535502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522385</t>
+          <t>521418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536108</t>
+          <t>535502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42937</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69690</t>
+          <t>70278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42937</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69690</t>
+          <t>70278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1168644</t>
+          <t>1168056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1195397</t>
+          <t>1195894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1168644</t>
+          <t>1168056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1195397</t>
+          <t>1195894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325117</t>
+          <t>323814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340801</t>
+          <t>339613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>325117</t>
+          <t>323814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>340801</t>
+          <t>339613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293587</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293587</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87704</t>
+          <t>87677</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125884</t>
+          <t>125859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87704</t>
+          <t>87677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125884</t>
+          <t>125859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3144306</t>
+          <t>3144331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3182486</t>
+          <t>3182513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3144306</t>
+          <t>3144331</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3182486</t>
+          <t>3182513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408782</t>
+          <t>409239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427410</t>
+          <t>426738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408782</t>
+          <t>409239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427410</t>
+          <t>426738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389060</t>
+          <t>387478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407391</t>
+          <t>406993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389060</t>
+          <t>387478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>407391</t>
+          <t>406993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589181</t>
+          <t>589660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613033</t>
+          <t>612996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589181</t>
+          <t>589660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>613033</t>
+          <t>612996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30555</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55839</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30555</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55839</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1103170</t>
+          <t>1103944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1128454</t>
+          <t>1129861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1103170</t>
+          <t>1103944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1128454</t>
+          <t>1129861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>476443</t>
+          <t>476347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495313</t>
+          <t>495361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476443</t>
+          <t>476347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495313</t>
+          <t>495361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101106</t>
+          <t>103285</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149196</t>
+          <t>148428</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101106</t>
+          <t>103285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149196</t>
+          <t>148428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3270522</t>
+          <t>3271290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3318612</t>
+          <t>3316433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3270522</t>
+          <t>3271290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3318612</t>
+          <t>3316433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23468</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23468</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405624</t>
+          <t>405536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420598</t>
+          <t>420643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405624</t>
+          <t>405536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420598</t>
+          <t>420643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24281</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24281</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352946</t>
+          <t>351652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369256</t>
+          <t>368712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352946</t>
+          <t>351652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369256</t>
+          <t>368712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491813</t>
+          <t>491330</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508740</t>
+          <t>509134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>491813</t>
+          <t>491330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>508740</t>
+          <t>509134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>38917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>38917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1110524</t>
+          <t>1110721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1129776</t>
+          <t>1130528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1110524</t>
+          <t>1110721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1129776</t>
+          <t>1130528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>579183</t>
+          <t>578135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>599618</t>
+          <t>598522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>579183</t>
+          <t>578135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>599618</t>
+          <t>598522</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90174</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130817</t>
+          <t>129904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90174</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130817</t>
+          <t>129904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3254905</t>
+          <t>3255818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3295548</t>
+          <t>3295606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3254905</t>
+          <t>3255818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3295548</t>
+          <t>3295606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6185,22 +6185,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38666</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6220,22 +6220,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38666</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -6263,27 +6263,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>471463</t>
+          <t>513795</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461426</t>
+          <t>504148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>478811</t>
+          <t>522125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6298,27 +6298,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>471463</t>
+          <t>513795</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461426</t>
+          <t>504148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>478811</t>
+          <t>522125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>545379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>545379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>545379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6376,17 +6376,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>545379</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>545379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>545379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6501,32 +6501,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423190</t>
+          <t>452435</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412457</t>
+          <t>441624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431186</t>
+          <t>460996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6536,32 +6536,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>423190</t>
+          <t>452435</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412457</t>
+          <t>441624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431186</t>
+          <t>460996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451117</t>
+          <t>482002</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451117</t>
+          <t>482002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451117</t>
+          <t>482002</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451117</t>
+          <t>482002</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>451117</t>
+          <t>482002</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>451117</t>
+          <t>482002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6661,32 +6661,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6696,32 +6696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6739,32 +6739,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>638582</t>
+          <t>439557</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616135</t>
+          <t>430124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656181</t>
+          <t>447261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6774,32 +6774,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>638582</t>
+          <t>439557</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616135</t>
+          <t>430124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656181</t>
+          <t>447261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666799</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666799</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666799</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>666799</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>666799</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>666799</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6899,32 +6899,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63368</t>
+          <t>67666</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51598</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6934,32 +6934,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63368</t>
+          <t>67666</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51598</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -6977,32 +6977,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>962678</t>
+          <t>1055339</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>949068</t>
+          <t>1039461</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>1067451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7012,32 +7012,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>962678</t>
+          <t>1055339</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>949068</t>
+          <t>1039461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>1067451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -7055,17 +7055,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1026046</t>
+          <t>1123005</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1026046</t>
+          <t>1123005</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1026046</t>
+          <t>1123005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7090,17 +7090,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1026046</t>
+          <t>1123005</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1026046</t>
+          <t>1123005</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1026046</t>
+          <t>1123005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7137,32 +7137,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7172,32 +7172,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>444535</t>
+          <t>535861</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435150</t>
+          <t>526308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451827</t>
+          <t>543552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7250,32 +7250,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>444535</t>
+          <t>535861</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435150</t>
+          <t>526308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451827</t>
+          <t>543552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>471693</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>471693</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471693</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7328,17 +7328,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>471693</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>471693</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>471693</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7453,27 +7453,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239270</t>
+          <t>236001</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235381</t>
+          <t>232766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7488,27 +7488,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>239270</t>
+          <t>236001</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235381</t>
+          <t>232766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7613,32 +7613,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>176535</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138563</t>
+          <t>166841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204154</t>
+          <t>212441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7648,32 +7648,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>176535</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138563</t>
+          <t>166841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204154</t>
+          <t>212441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -7691,32 +7691,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3179720</t>
+          <t>3232989</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3152101</t>
+          <t>3209533</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3217692</t>
+          <t>3255133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7726,32 +7726,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3179720</t>
+          <t>3232989</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3152101</t>
+          <t>3209533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3217692</t>
+          <t>3255133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3356255</t>
+          <t>3421974</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3356255</t>
+          <t>3421974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3356255</t>
+          <t>3421974</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3356255</t>
+          <t>3421974</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3356255</t>
+          <t>3421974</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3356255</t>
+          <t>3421974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
